--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/orders.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/orders.xlsx
@@ -413,21 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>order_date</t>
         </is>
@@ -438,12 +458,24 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>101</v>
       </c>
-      <c r="C2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
@@ -454,12 +486,24 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>102</v>
       </c>
-      <c r="C3" t="n">
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-01-11</t>
         </is>
@@ -470,12 +514,24 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>103</v>
       </c>
-      <c r="C4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
@@ -486,12 +542,24 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>104</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
@@ -502,12 +570,24 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>105</v>
       </c>
-      <c r="C6" t="n">
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
@@ -518,12 +598,24 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
         <v>106</v>
       </c>
-      <c r="C7" t="n">
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2026-01-25</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/orders.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/orders.xlsx
@@ -413,41 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.3</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.2</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>order_date</t>
         </is>
@@ -458,24 +438,12 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>101</v>
-      </c>
-      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
@@ -486,24 +454,12 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>102</v>
-      </c>
-      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-01-11</t>
         </is>
@@ -514,24 +470,12 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>103</v>
-      </c>
-      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
@@ -542,24 +486,12 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>104</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-01-18</t>
         </is>
@@ -570,24 +502,12 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>105</v>
-      </c>
-      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
@@ -598,24 +518,12 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>106</v>
-      </c>
-      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2026-01-25</t>
         </is>
